--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT CILINDRO - 19_01 M.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT CILINDRO - 19_01 M.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KIT PISTONS RT FAZER150 0,25 793609</t>
+          <t>KIT PISTONE RT FAZER150 0,25 793609</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1419,27 +1419,6 @@
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>751320985033</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CABEÇOTE MOTOR IRON TITAN150 2006 A 2008 183002</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT CILINDRO - 19_01 M.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT CILINDRO - 19_01 M.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,7 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,11 +492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,11 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -574,11 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -599,11 +572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -624,7 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -645,11 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -670,11 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +652,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -720,11 +672,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,7 +692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -766,11 +712,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -791,11 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -816,7 +752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -837,11 +772,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -862,7 +792,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -883,7 +812,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -904,7 +832,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -925,11 +852,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -950,7 +872,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -971,11 +892,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -996,11 +912,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1021,11 +932,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1038,7 +944,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KIT CILINDRO RIIE/MJL FAN TITAN CG150-190</t>
+          <t>KIT CILINDRO RIIE FAN TITAN CG150-190</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1046,7 +952,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1059,7 +964,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIT CILINDRO SMARTFOX/PEÇA+ SHINERAY PHOENIX GOLD </t>
+          <t xml:space="preserve">KIT CILINDRO SMARTFOX SHINERAY PHOENIX GOLD </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1067,7 +972,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1088,11 +992,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1113,7 +1012,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1134,11 +1032,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1159,7 +1052,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1180,11 +1072,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1205,11 +1092,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1230,11 +1112,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1255,11 +1132,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1280,11 +1152,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1292,41 +1159,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7899248404556</t>
+          <t>7909201050124</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KIT PISTAO 0.25 KMP FAN CG125 2019 A 2018 1103188</t>
+          <t>KIT CILINDRO KMP FAZER250 2006 A 2013</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>7899248115400</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KIT PISTAO 0.25 KMP CG TITAN 2002 KS 1102761</t>
+          <t>KIT CILINDRO RIIE PCX150</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1334,12 +1195,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7909201030027</t>
+          <t>06121-KVS-305</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIT PISTAO 0.25 KMP TITAN FAN CG150 </t>
+          <t>KIT CILINDRO COMPLETO ORIGINAL HONDA TITAN FAN160 2015</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1347,7 +1208,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1355,12 +1215,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0602883766525</t>
+          <t>6121-K62-305</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KIT PISTAO 0.75 IRON YS250 FAZER/ LANDER XTZ250 187837</t>
+          <t>KIT CILINDRO COMPLETTO ORIGINAL HONDA POP110 2016/ BIZ110 2016</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1368,57 +1228,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>0602883766518</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>KIT PISTAO 1.0 IRON YS250 FAZER/ XTZ250 LANDER 187838</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1000007936097</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>KIT PISTONE RT FAZER150 0,25 793609</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
